--- a/docs/downloads/04/tbl_other_act_sex_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_alaotra_ambatoharanana.xlsx
@@ -420,12 +420,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -466,12 +460,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>3.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -489,12 +477,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>3.1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -673,12 +655,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D14">
-        <v>3</v>
-      </c>
-      <c r="E14">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -788,12 +764,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -856,12 +826,6 @@
         <is>
           <t>Éleveur</t>
         </is>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>0.2</v>
       </c>
     </row>
     <row r="23">

--- a/docs/downloads/04/tbl_other_act_sex_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_alaotra_ambatoharanana.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,14 +394,8 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>31</v>
-      </c>
-      <c r="E2">
-        <v>47.7</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -417,7 +411,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
@@ -434,14 +428,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D4">
         <v>29</v>
       </c>
       <c r="E4">
-        <v>44.6</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -457,7 +451,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
@@ -474,7 +468,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
     </row>
@@ -491,37 +485,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>72.40000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E8">
-        <v>27.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
@@ -537,14 +531,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D9">
-        <v>405</v>
+        <v>71</v>
       </c>
       <c r="E9">
-        <v>46.2</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="10">
@@ -560,14 +554,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D10">
-        <v>27</v>
+        <v>289</v>
       </c>
       <c r="E10">
-        <v>3.1</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="11">
@@ -583,14 +577,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D11">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="E11">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12">
@@ -606,14 +600,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D12">
-        <v>289</v>
+        <v>26</v>
       </c>
       <c r="E12">
-        <v>33</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="13">
@@ -636,7 +630,7 @@
         <v>57</v>
       </c>
       <c r="E13">
-        <v>6.5</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="14">
@@ -652,8 +646,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>46</v>
+      </c>
+      <c r="E14">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -664,19 +664,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E15">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="16">
@@ -687,19 +687,13 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>26</v>
-      </c>
-      <c r="E16">
-        <v>3</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -715,14 +709,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D17">
-        <v>418</v>
+        <v>101</v>
       </c>
       <c r="E17">
-        <v>71.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="18">
@@ -738,14 +732,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D18">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E18">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="19">
@@ -761,8 +755,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>25</v>
+      </c>
+      <c r="E19">
+        <v>11.8</v>
       </c>
     </row>
     <row r="20">
@@ -778,14 +778,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D20">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="E20">
-        <v>17.3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -801,54 +801,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D21">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E21">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>25</v>
-      </c>
-      <c r="E23">
-        <v>4.3</v>
+        <v>17.9</v>
       </c>
     </row>
   </sheetData>
